--- a/288/food/tm2026-sm.xlsx
+++ b/288/food/tm2026-sm.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -448,6 +448,30 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -478,35 +502,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -646,6 +646,9 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -656,6 +659,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -669,27 +681,18 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1072,8 +1075,8 @@
   <cols>
     <col width="4.7109375" customWidth="1" style="2" min="1" max="1"/>
     <col width="5.28515625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="9.140625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="11.5703125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9.140625" customWidth="1" style="50" min="3" max="3"/>
+    <col width="11.5703125" customWidth="1" style="50" min="4" max="4"/>
     <col width="52.5703125" customWidth="1" style="2" min="5" max="5"/>
     <col width="9.28515625" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="7"/>
@@ -1085,18 +1088,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Школа</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>МБОУ «СОШ №2 с.Новые Атаги»</t>
         </is>
       </c>
-      <c r="D1" s="59" t="n"/>
-      <c r="E1" s="60" t="n"/>
+      <c r="D1" s="60" t="n"/>
+      <c r="E1" s="61" t="n"/>
       <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Утвердил:</t>
@@ -1107,14 +1110,14 @@
           <t>должность</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Директор</t>
         </is>
       </c>
-      <c r="I1" s="59" t="n"/>
-      <c r="J1" s="59" t="n"/>
-      <c r="K1" s="60" t="n"/>
+      <c r="I1" s="60" t="n"/>
+      <c r="J1" s="60" t="n"/>
+      <c r="K1" s="61" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
@@ -1128,14 +1131,14 @@
           <t>фамилия</t>
         </is>
       </c>
-      <c r="H2" s="55" t="inlineStr">
+      <c r="H2" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">Керимова Зарган Алиевна </t>
         </is>
       </c>
-      <c r="I2" s="59" t="n"/>
-      <c r="J2" s="59" t="n"/>
-      <c r="K2" s="60" t="n"/>
+      <c r="I2" s="60" t="n"/>
+      <c r="J2" s="60" t="n"/>
+      <c r="K2" s="61" t="n"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1164,7 +1167,7 @@
       <c r="J3" s="49" t="n">
         <v>2026</v>
       </c>
-      <c r="K3" s="1" t="n"/>
+      <c r="K3" s="50" t="n"/>
     </row>
     <row r="4" ht="13.5" customHeight="1" thickBot="1">
       <c r="C4" s="2" t="n"/>
@@ -1295,7 +1298,7 @@
       <c r="A7" s="23" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="11" t="n"/>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
@@ -1794,12 +1797,12 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C24" s="61" t="inlineStr">
+      <c r="C24" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D24" s="62" t="n"/>
+      <c r="D24" s="63" t="n"/>
       <c r="E24" s="31" t="n"/>
       <c r="F24" s="32">
         <f>F13+F23</f>
@@ -1867,7 +1870,7 @@
       <c r="K25" s="41" t="n">
         <v>177</v>
       </c>
-      <c r="L25" s="51" t="n">
+      <c r="L25" s="52" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1917,7 +1920,7 @@
       <c r="K27" s="44" t="n">
         <v>378</v>
       </c>
-      <c r="L27" s="52" t="n">
+      <c r="L27" s="53" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1951,7 +1954,7 @@
         <v>116.82</v>
       </c>
       <c r="K28" s="44" t="n"/>
-      <c r="L28" s="52" t="n">
+      <c r="L28" s="53" t="n">
         <v>8.77</v>
       </c>
     </row>
@@ -1987,7 +1990,7 @@
       <c r="K29" s="44" t="n">
         <v>338</v>
       </c>
-      <c r="L29" s="52" t="n">
+      <c r="L29" s="53" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2350,12 +2353,12 @@
         <f>B25</f>
         <v/>
       </c>
-      <c r="C43" s="61" t="inlineStr">
+      <c r="C43" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D43" s="62" t="n"/>
+      <c r="D43" s="63" t="n"/>
       <c r="E43" s="31" t="n"/>
       <c r="F43" s="32">
         <f>F32+F42</f>
@@ -2966,12 +2969,12 @@
         <f>B44</f>
         <v/>
       </c>
-      <c r="C62" s="61" t="inlineStr">
+      <c r="C62" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D62" s="62" t="n"/>
+      <c r="D62" s="63" t="n"/>
       <c r="E62" s="31" t="n"/>
       <c r="F62" s="32">
         <f>F51+F61</f>
@@ -3542,12 +3545,12 @@
         <f>B63</f>
         <v/>
       </c>
-      <c r="C81" s="61" t="inlineStr">
+      <c r="C81" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D81" s="62" t="n"/>
+      <c r="D81" s="63" t="n"/>
       <c r="E81" s="31" t="n"/>
       <c r="F81" s="32">
         <f>F70+F80</f>
@@ -4126,12 +4129,12 @@
         <f>B82</f>
         <v/>
       </c>
-      <c r="C100" s="61" t="inlineStr">
+      <c r="C100" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D100" s="62" t="n"/>
+      <c r="D100" s="63" t="n"/>
       <c r="E100" s="31" t="n"/>
       <c r="F100" s="32">
         <f>F89+F99</f>
@@ -4494,7 +4497,7 @@
         <v>83</v>
       </c>
       <c r="L110" s="43" t="n">
-        <v>25.52</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
@@ -4654,7 +4657,7 @@
         <v>14</v>
       </c>
       <c r="L115" s="44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
@@ -4730,12 +4733,12 @@
         <f>B101</f>
         <v/>
       </c>
-      <c r="C119" s="61" t="inlineStr">
+      <c r="C119" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D119" s="62" t="n"/>
+      <c r="D119" s="63" t="n"/>
       <c r="E119" s="31" t="n"/>
       <c r="F119" s="32">
         <f>F108+F118</f>
@@ -4924,7 +4927,7 @@
         <v>338</v>
       </c>
       <c r="L124" s="43" t="n">
-        <v>16.35</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -4959,9 +4962,7 @@
       <c r="K125" s="44" t="n">
         <v>14</v>
       </c>
-      <c r="L125" s="43" t="n">
-        <v>2</v>
-      </c>
+      <c r="L125" s="43" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="14" t="n"/>
@@ -5308,12 +5309,12 @@
         <f>B120</f>
         <v/>
       </c>
-      <c r="C138" s="61" t="inlineStr">
+      <c r="C138" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D138" s="62" t="n"/>
+      <c r="D138" s="63" t="n"/>
       <c r="E138" s="31" t="n"/>
       <c r="F138" s="32">
         <f>F127+F137</f>
@@ -5886,12 +5887,12 @@
         <f>B139</f>
         <v/>
       </c>
-      <c r="C157" s="61" t="inlineStr">
+      <c r="C157" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D157" s="62" t="n"/>
+      <c r="D157" s="63" t="n"/>
       <c r="E157" s="31" t="n"/>
       <c r="F157" s="32">
         <f>F146+F156</f>
@@ -6464,12 +6465,12 @@
         <f>B158</f>
         <v/>
       </c>
-      <c r="C176" s="61" t="inlineStr">
+      <c r="C176" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D176" s="62" t="n"/>
+      <c r="D176" s="63" t="n"/>
       <c r="E176" s="31" t="n"/>
       <c r="F176" s="32">
         <f>F165+F175</f>
@@ -7040,12 +7041,12 @@
         <f>B177</f>
         <v/>
       </c>
-      <c r="C195" s="61" t="inlineStr">
+      <c r="C195" s="62" t="inlineStr">
         <is>
           <t>Итого за день:</t>
         </is>
       </c>
-      <c r="D195" s="62" t="n"/>
+      <c r="D195" s="63" t="n"/>
       <c r="E195" s="31" t="n"/>
       <c r="F195" s="32">
         <f>F184+F194</f>
@@ -7076,13 +7077,13 @@
     <row r="196" ht="13.5" customHeight="1" thickBot="1">
       <c r="A196" s="27" t="n"/>
       <c r="B196" s="28" t="n"/>
-      <c r="C196" s="58" t="inlineStr">
+      <c r="C196" s="56" t="inlineStr">
         <is>
           <t>Среднее значение за период:</t>
         </is>
       </c>
-      <c r="D196" s="63" t="n"/>
-      <c r="E196" s="64" t="n"/>
+      <c r="D196" s="64" t="n"/>
+      <c r="E196" s="65" t="n"/>
       <c r="F196" s="34">
         <f>(F24+F43+F62+F81+F100+F119+F138+F157+F176+F195)/(IF(F24=0,0,1)+IF(F43=0,0,1)+IF(F62=0,0,1)+IF(F81=0,0,1)+IF(F100=0,0,1)+IF(F119=0,0,1)+IF(F138=0,0,1)+IF(F157=0,0,1)+IF(F176=0,0,1)+IF(F195=0,0,1))</f>
         <v/>
@@ -7113,11 +7114,11 @@
   <mergeCells count="14">
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C138:D138"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="H2:K2"/>

--- a/288/food/tm2026-sm.xlsx
+++ b/288/food/tm2026-sm.xlsx
@@ -7114,8 +7114,8 @@
   <mergeCells count="14">
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C100:D100"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
